--- a/vocabolario_V2.4.xlsx
+++ b/vocabolario_V2.4.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{618F205A-6899-41C9-847B-DC7E543AE5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2913ED5B-2D83-4817-BE03-39B880D2A644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="868" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -40,13 +40,14 @@
     <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId25"/>
     <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId26"/>
     <sheet name="Numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId27"/>
+    <sheet name="Traffico | Verkehr" sheetId="29" r:id="rId28"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="1858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="1915">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -5700,6 +5701,177 @@
   </si>
   <si>
     <t>hundertfünfundzwanzigste/r (125.)</t>
+  </si>
+  <si>
+    <t>Vocabolario</t>
+  </si>
+  <si>
+    <t>andare dritto</t>
+  </si>
+  <si>
+    <t>geradeaus gehen</t>
+  </si>
+  <si>
+    <t>Verkehr</t>
+  </si>
+  <si>
+    <t>girare a sinstra</t>
+  </si>
+  <si>
+    <t>links abbiegen</t>
+  </si>
+  <si>
+    <t>girare a destra</t>
+  </si>
+  <si>
+    <t>rechts abbiegen</t>
+  </si>
+  <si>
+    <t>tornare indietro</t>
+  </si>
+  <si>
+    <t>zurückgehen/umkehren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attraversare la strada </t>
+  </si>
+  <si>
+    <t>die Straße überqueren</t>
+  </si>
+  <si>
+    <t>prendere la seconda traversa a destra</t>
+  </si>
+  <si>
+    <t>die zweite Straße rechts nehmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrivare al semaforo </t>
+  </si>
+  <si>
+    <t>zur Ampel kommen</t>
+  </si>
+  <si>
+    <t>superare l´icrocio</t>
+  </si>
+  <si>
+    <t>die Kreuzung überqueren</t>
+  </si>
+  <si>
+    <t>il semaforo</t>
+  </si>
+  <si>
+    <t>Ampel</t>
+  </si>
+  <si>
+    <t>l'incrocio</t>
+  </si>
+  <si>
+    <t>Kreuzung</t>
+  </si>
+  <si>
+    <t>lo spartitraffico</t>
+  </si>
+  <si>
+    <t>Mittelstreifen</t>
+  </si>
+  <si>
+    <t>la strada</t>
+  </si>
+  <si>
+    <t>Straße</t>
+  </si>
+  <si>
+    <t>il traffico</t>
+  </si>
+  <si>
+    <t>l'ingorgo</t>
+  </si>
+  <si>
+    <t>Stau</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Fahrrad</t>
+  </si>
+  <si>
+    <t>il pedone</t>
+  </si>
+  <si>
+    <t>Fußgänger</t>
+  </si>
+  <si>
+    <t>fermarsi al semaforo</t>
+  </si>
+  <si>
+    <t>an der Ampel anhalten</t>
+  </si>
+  <si>
+    <t>parcheggiare la macchina</t>
+  </si>
+  <si>
+    <t>das Auto parken</t>
+  </si>
+  <si>
+    <t>attraversare sulle strisce</t>
+  </si>
+  <si>
+    <t>auf dem Zebrastreifen überqueren</t>
+  </si>
+  <si>
+    <t>il marciapiede</t>
+  </si>
+  <si>
+    <t>der Bürgersteig</t>
+  </si>
+  <si>
+    <t>le strisce pedonali</t>
+  </si>
+  <si>
+    <t>der Zebrastreifen</t>
+  </si>
+  <si>
+    <t>il limite di velocità</t>
+  </si>
+  <si>
+    <t>das Tempolimit</t>
+  </si>
+  <si>
+    <t>la multa</t>
+  </si>
+  <si>
+    <t>der Strafzettel</t>
+  </si>
+  <si>
+    <t>il parcheggio</t>
+  </si>
+  <si>
+    <t>der Parkplatz</t>
+  </si>
+  <si>
+    <t>la rotonda</t>
+  </si>
+  <si>
+    <t>der Kreisverkehr</t>
+  </si>
+  <si>
+    <t>il vigile</t>
+  </si>
+  <si>
+    <t>der Verkehrspolizist</t>
+  </si>
+  <si>
+    <t>la patente</t>
+  </si>
+  <si>
+    <t>der Führerschein</t>
+  </si>
+  <si>
+    <t>la cintura di sicurezza</t>
+  </si>
+  <si>
+    <t>der Sicherheitsgurt</t>
   </si>
 </sst>
 </file>
@@ -5798,7 +5970,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5817,12 +5989,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -6140,6 +6315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -6150,6 +6326,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr codeName="Tabelle10"/>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6159,7 +6336,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>735</v>
       </c>
       <c r="B1" s="13"/>
@@ -6170,7 +6347,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>736</v>
       </c>
       <c r="B2" s="13"/>
@@ -6576,6 +6753,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr codeName="Tabelle11"/>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6585,7 +6763,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>813</v>
       </c>
       <c r="B1" s="13"/>
@@ -6596,7 +6774,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>814</v>
       </c>
       <c r="B2" s="13"/>
@@ -6858,6 +7036,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr codeName="Tabelle12"/>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6867,7 +7046,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>850</v>
       </c>
       <c r="B1" s="13"/>
@@ -6878,7 +7057,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>851</v>
       </c>
       <c r="B2" s="13"/>
@@ -7493,6 +7672,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr codeName="Tabelle13"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7502,7 +7682,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>973</v>
       </c>
       <c r="B1" s="13"/>
@@ -7513,7 +7693,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -7843,6 +8023,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr codeName="Tabelle14"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7852,7 +8033,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1035</v>
       </c>
       <c r="B1" s="13"/>
@@ -7863,7 +8044,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -8193,6 +8374,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr codeName="Tabelle15"/>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8202,7 +8384,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1097</v>
       </c>
       <c r="B1" s="13"/>
@@ -8213,7 +8395,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -8638,6 +8820,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr codeName="Tabelle16"/>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8647,7 +8830,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1179</v>
       </c>
       <c r="B1" s="13"/>
@@ -8658,7 +8841,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -9064,6 +9247,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr codeName="Tabelle17"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9073,7 +9257,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1250</v>
       </c>
       <c r="B1" s="13"/>
@@ -9084,7 +9268,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -9414,6 +9598,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr codeName="Tabelle18"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9423,7 +9608,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1311</v>
       </c>
       <c r="B1" s="13"/>
@@ -9434,7 +9619,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -9764,6 +9949,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <sheetPr codeName="Tabelle19"/>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -9773,7 +9959,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1373</v>
       </c>
       <c r="B1" s="13"/>
@@ -9784,7 +9970,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -10019,6 +10205,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10029,7 +10216,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="13"/>
@@ -10040,7 +10227,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>42</v>
       </c>
       <c r="B2" s="13"/>
@@ -10748,6 +10935,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <sheetPr codeName="Tabelle20"/>
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10757,7 +10945,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1415</v>
       </c>
       <c r="B1" s="13"/>
@@ -10768,7 +10956,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -11288,6 +11476,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <sheetPr codeName="Tabelle21"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11297,7 +11486,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1515</v>
       </c>
       <c r="B1" s="13"/>
@@ -11308,7 +11497,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -11638,6 +11827,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <sheetPr codeName="Tabelle22"/>
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11647,7 +11837,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1576</v>
       </c>
       <c r="B1" s="13"/>
@@ -11658,7 +11848,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -11836,6 +12026,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <sheetPr codeName="Tabelle23"/>
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11845,7 +12036,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
@@ -11856,7 +12047,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -12053,6 +12244,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <sheetPr codeName="Tabelle24"/>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12062,7 +12254,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1606</v>
       </c>
       <c r="B1" s="13"/>
@@ -12073,7 +12265,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -12403,6 +12595,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+  <sheetPr codeName="Tabelle25"/>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12412,7 +12605,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1668</v>
       </c>
       <c r="B1" s="13"/>
@@ -12423,7 +12616,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -12696,6 +12889,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+  <sheetPr codeName="Tabelle26"/>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12705,7 +12899,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1718</v>
       </c>
       <c r="B1" s="13"/>
@@ -12716,7 +12910,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -13125,6 +13319,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
+  <sheetPr codeName="Tabelle27"/>
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13134,7 +13329,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>1778</v>
       </c>
       <c r="B1" s="13"/>
@@ -13145,7 +13340,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
@@ -13672,8 +13867,399 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1DFE71-12D1-41EA-98DC-C392F6CEA66F}">
+  <sheetPr codeName="Tabelle28"/>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="7" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14079,6 +14665,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14092,7 +14679,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>197</v>
       </c>
       <c r="B1" s="13"/>
@@ -14103,7 +14690,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>198</v>
       </c>
       <c r="B2" s="13"/>
@@ -14269,6 +14856,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14280,7 +14868,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>197</v>
       </c>
       <c r="B1" s="13"/>
@@ -14291,7 +14879,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>198</v>
       </c>
       <c r="B2" s="13"/>
@@ -14678,6 +15266,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14688,7 +15277,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>294</v>
       </c>
       <c r="B1" s="13"/>
@@ -14699,7 +15288,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>295</v>
       </c>
       <c r="B2" s="13"/>
@@ -15118,6 +15707,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15127,7 +15717,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>385</v>
       </c>
       <c r="B1" s="13"/>
@@ -15138,7 +15728,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>386</v>
       </c>
       <c r="B2" s="13"/>
@@ -15620,6 +16210,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Tabelle8"/>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15630,7 +16221,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>482</v>
       </c>
       <c r="B1" s="13"/>
@@ -15641,7 +16232,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>483</v>
       </c>
       <c r="B2" s="13"/>
@@ -16256,6 +16847,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="Tabelle9"/>
   <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16265,7 +16857,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>572</v>
       </c>
       <c r="B1" s="13"/>
@@ -16276,7 +16868,7 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="13"/>
